--- a/SwagLabs_Manual_Test_Suite_Hridaya.xlsx
+++ b/SwagLabs_Manual_Test_Suite_Hridaya.xlsx
@@ -4,8 +4,8 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Test Scenario" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Login" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Logout" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Logout" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Login" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="Shopping Cart and UI" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="265">
   <si>
     <t>Project Name</t>
   </si>
@@ -121,10 +121,214 @@
     <t>Comments</t>
   </si>
   <si>
+    <t>TC_LGO_001</t>
+  </si>
+  <si>
+    <t>Validate the application by logging out</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>Open the application URL "</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.saucedemo.com/</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>" in any supported browser .
+Login with valid credentials</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Click on the hamburger menu icon on the top left corner
+2. Click on the logout link from side menu</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>User should be logged out</t>
+  </si>
+  <si>
+    <t>User logged out</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>TC_LGO_002</t>
+  </si>
+  <si>
+    <t>Validate logging out by pressing the browser back button after logging out</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>Open the application URL "</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.saucedemo.com/</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>" in any supported browser
+Login with valid credentials</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click on the hamburger menu icon on the top left corner
+2. Click on the logout link from side menu
+3. Click on the browser back button
+</t>
+  </si>
+  <si>
+    <t>User logged out with message:"Epic sadface: You can only access '/inventory.html' when you are logged in."</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>TC_LGO_003</t>
+  </si>
+  <si>
+    <t>Validate logging out from one  device after logging into different devices</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>Open the application URL "</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.saucedemo.com/</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t xml:space="preserve">" in any supported browser in your laptop and mobile
+Login with valid credentials </t>
+    </r>
+  </si>
+  <si>
+    <t>1. Logout from laptop window
+3. Try to navigate to other links from mobile window</t>
+  </si>
+  <si>
+    <t>User should be logged out from the other device also</t>
+  </si>
+  <si>
+    <t>User not logged out from the other device</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>TC_LGO_004</t>
+  </si>
+  <si>
+    <t>Validate logout functionality in all supported browsers</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>Open the application URL "</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.saucedemo.com/</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>" in any supported browser
+Login with valid credentials</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Click on the hamburger menu icon on the top left corner
+2. Click on the logout link from side menu
+3. Try in chrome and edge browsers</t>
+  </si>
+  <si>
+    <t>User should be logged out from different browsers</t>
+  </si>
+  <si>
+    <t>User logged out from different browsers</t>
+  </si>
+  <si>
+    <t>TC_LGO_005</t>
+  </si>
+  <si>
+    <t>Validate logout functionality by logging in and then closing browser without logging out and  see if the user is logged out</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>Open the application URL "</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.saucedemo.com/</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>" in any supported browser
+Login with valid credentials</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Close the window
+2. Open the site again and see if user is logged out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be logged out </t>
+  </si>
+  <si>
+    <t xml:space="preserve">User logged out from the site </t>
+  </si>
+  <si>
     <t>Attachments</t>
-  </si>
-  <si>
-    <t>To validte the Login functionality</t>
   </si>
   <si>
     <t>TC_LG_001</t>
@@ -165,9 +369,6 @@
   </si>
   <si>
     <t>User logged in</t>
-  </si>
-  <si>
-    <t>Pass</t>
   </si>
   <si>
     <t>Password breach message displayed  and prompted to change password. Screenshot attached</t>
@@ -529,9 +730,6 @@
     <t>User should not be logged in with error message showing "invalid username and password"</t>
   </si>
   <si>
-    <t>P3</t>
-  </si>
-  <si>
     <t>TC_LG_011</t>
   </si>
   <si>
@@ -647,207 +845,6 @@
   </si>
   <si>
     <t>Password typed in the password field is toggled</t>
-  </si>
-  <si>
-    <t>TC_LGO_001</t>
-  </si>
-  <si>
-    <t>Validate the application by logging out</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-      </rPr>
-      <t>Open the application URL "</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.saucedemo.com/</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-      </rPr>
-      <t>" in any supported browser .
-Login with valid credentials</t>
-    </r>
-  </si>
-  <si>
-    <t>1. Click on the hamburger menu icon on the top left corner
-2. Click on the logout link from side menu</t>
-  </si>
-  <si>
-    <t>Not applicable</t>
-  </si>
-  <si>
-    <t>User should be logged out</t>
-  </si>
-  <si>
-    <t>User logged out</t>
-  </si>
-  <si>
-    <t>TC_LGO_002</t>
-  </si>
-  <si>
-    <t>Validate logging out by pressing the browser back button after logging out</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-      </rPr>
-      <t>Open the application URL "</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.saucedemo.com/</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-      </rPr>
-      <t>" in any supported browser
-Login with valid credentials</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click on the hamburger menu icon on the top left corner
-2. Click on the logout link from side menu
-3. Click on the browser back button
-</t>
-  </si>
-  <si>
-    <t>User logged out with message:"Epic sadface: You can only access '/inventory.html' when you are logged in."</t>
-  </si>
-  <si>
-    <t>TC_LGO_003</t>
-  </si>
-  <si>
-    <t>Validate logging out from one  device after logging into different devices</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-      </rPr>
-      <t>Open the application URL "</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.saucedemo.com/</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-      </rPr>
-      <t xml:space="preserve">" in any supported browser in your laptop and mobile
-Login with valid credentials </t>
-    </r>
-  </si>
-  <si>
-    <t>1. Logout from laptop window
-3. Try to navigate to other links from mobile window</t>
-  </si>
-  <si>
-    <t>User should be logged out from the other device also</t>
-  </si>
-  <si>
-    <t>User not logged out from the other device</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>TC_LGO_004</t>
-  </si>
-  <si>
-    <t>Validate logout functionality in all supported browsers</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-      </rPr>
-      <t>Open the application URL "</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.saucedemo.com/</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-      </rPr>
-      <t>" in any supported browser
-Login with valid credentials</t>
-    </r>
-  </si>
-  <si>
-    <t>1. Click on the hamburger menu icon on the top left corner
-2. Click on the logout link from side menu
-3. Try in chrome and edge browsers</t>
-  </si>
-  <si>
-    <t>User should be logged out from different browsers</t>
-  </si>
-  <si>
-    <t>User logged out from different browsers</t>
-  </si>
-  <si>
-    <t>TC_LGO_005</t>
-  </si>
-  <si>
-    <t>Validate logout functionality by logging in and then closing browser without logging out and  see if the user is logged out</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-      </rPr>
-      <t>Open the application URL "</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>https://www.saucedemo.com/</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Verdana"/>
-      </rPr>
-      <t>" in any supported browser
-Login with valid credentials</t>
-    </r>
-  </si>
-  <si>
-    <t>1. Close the window
-2. Open the site again and see if user is logged out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User should be logged out </t>
-  </si>
-  <si>
-    <t xml:space="preserve">User logged out from the site </t>
   </si>
   <si>
     <t>To validate the Shopping cart functionality</t>
@@ -1905,9 +1902,6 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1918,6 +1912,21 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1926,20 +1935,8 @@
     <xf borderId="0" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="8" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2010,13 +2007,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="3">
-    <tableStyle count="4" pivot="0" name="Login-style">
+    <tableStyle count="4" pivot="0" name="Logout-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Logout-style">
+    <tableStyle count="4" pivot="0" name="Login-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -2053,7 +2050,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L18" displayName="Table1" name="Table1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:K7" displayName="Table2" name="Table2" id="1">
+  <tableColumns count="11">
+    <tableColumn name="Test Scenario" id="1"/>
+    <tableColumn name="Test Case ID" id="2"/>
+    <tableColumn name="Test Case description" id="3"/>
+    <tableColumn name="Preconditions" id="4"/>
+    <tableColumn name="Test Steps" id="5"/>
+    <tableColumn name="Test Data" id="6"/>
+    <tableColumn name="Expected Result" id="7"/>
+    <tableColumn name="Actual Result" id="8"/>
+    <tableColumn name="Priority" id="9"/>
+    <tableColumn name="Result" id="10"/>
+    <tableColumn name="Comments" id="11"/>
+  </tableColumns>
+  <tableStyleInfo name="Logout-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L18" displayName="Table1" name="Table1" id="2">
   <tableColumns count="12">
     <tableColumn name="Test Scenario" id="1"/>
     <tableColumn name="Test Case ID" id="2"/>
@@ -2069,25 +2085,6 @@
     <tableColumn name="Attachments" id="12"/>
   </tableColumns>
   <tableStyleInfo name="Login-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:K7" displayName="Table2" name="Table2" id="2">
-  <tableColumns count="11">
-    <tableColumn name="Test Scenario" id="1"/>
-    <tableColumn name="Test Case ID" id="2"/>
-    <tableColumn name="Test Case description" id="3"/>
-    <tableColumn name="Preconditions" id="4"/>
-    <tableColumn name="Test Steps" id="5"/>
-    <tableColumn name="Test Data" id="6"/>
-    <tableColumn name="Expected Result" id="7"/>
-    <tableColumn name="Actual Result" id="8"/>
-    <tableColumn name="Priority" id="9"/>
-    <tableColumn name="Result" id="10"/>
-    <tableColumn name="Comments" id="11"/>
-  </tableColumns>
-  <tableStyleInfo name="Logout-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -2472,6 +2469,247 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="18.0"/>
+    <col customWidth="1" min="4" max="4" width="17.0"/>
+    <col customWidth="1" min="5" max="5" width="21.38"/>
+    <col customWidth="1" min="6" max="6" width="13.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22.5" customHeight="1">
+      <c r="A1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="19"/>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="19"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="19"/>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="19"/>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="19"/>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="D2"/>
+    <hyperlink r:id="rId2" ref="D3"/>
+    <hyperlink r:id="rId3" ref="D4"/>
+    <hyperlink r:id="rId4" ref="D5"/>
+    <hyperlink r:id="rId5" ref="D6"/>
+  </hyperlinks>
+  <drawing r:id="rId6"/>
+  <tableParts count="1">
+    <tablePart r:id="rId8"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
@@ -2517,509 +2755,509 @@
       <c r="K1" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="16" t="s">
-        <v>35</v>
+      <c r="L1" s="23" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="20" t="s">
+      <c r="A2" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="K2" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="26"/>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" s="22"/>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="K3" s="19"/>
+      <c r="L3" s="22"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="19"/>
+      <c r="L4" s="22"/>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="19"/>
+      <c r="L5" s="22"/>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="19"/>
+      <c r="L6" s="22"/>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="19"/>
+      <c r="L7" s="22"/>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="19"/>
+      <c r="L8" s="22"/>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="19"/>
+      <c r="L9" s="22"/>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="19"/>
+      <c r="L10" s="22"/>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="23"/>
-      <c r="L3" s="24"/>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="23"/>
-      <c r="L4" s="24"/>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="23"/>
-      <c r="L5" s="24"/>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="23"/>
-      <c r="L6" s="24"/>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="24"/>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="24"/>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" s="23"/>
-      <c r="L9" s="24"/>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="23"/>
-      <c r="L10" s="24"/>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" s="23"/>
-      <c r="L11" s="24"/>
+      <c r="J11" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="19"/>
+      <c r="L11" s="22"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K12" s="23"/>
-      <c r="L12" s="24"/>
+      <c r="A12" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="19"/>
+      <c r="L12" s="22"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" s="23"/>
-      <c r="L13" s="24"/>
+      <c r="A13" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" s="19"/>
+      <c r="L13" s="22"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" s="23"/>
-      <c r="L14" s="24"/>
+      <c r="A14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14" s="19"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="17"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="27"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="20"/>
       <c r="D15" s="28"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="17"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="27"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="28"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="17"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="27"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="28"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="17"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="27"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="28"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3047,247 +3285,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="3" max="3" width="18.0"/>
-    <col customWidth="1" min="4" max="4" width="17.0"/>
-    <col customWidth="1" min="5" max="5" width="21.38"/>
-    <col customWidth="1" min="6" max="6" width="13.0"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
-      <c r="A1" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="23"/>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="23"/>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="K4" s="23"/>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="23"/>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="23"/>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="D2"/>
-    <hyperlink r:id="rId2" ref="D3"/>
-    <hyperlink r:id="rId3" ref="D4"/>
-    <hyperlink r:id="rId4" ref="D5"/>
-    <hyperlink r:id="rId5" ref="D6"/>
-  </hyperlinks>
-  <drawing r:id="rId6"/>
-  <tableParts count="1">
-    <tablePart r:id="rId8"/>
-  </tableParts>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
@@ -3341,677 +3338,677 @@
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="C2" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="D2" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="E2" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="F2" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="F2" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="21" t="s">
+      <c r="H2" s="25" t="s">
         <v>155</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>156</v>
       </c>
       <c r="I2" s="30" t="s">
         <v>19</v>
       </c>
       <c r="J2" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K2" s="22"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="D3" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="E3" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="F3" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3" s="21" t="s">
+      <c r="H3" s="25" t="s">
         <v>161</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>162</v>
       </c>
       <c r="I3" s="30" t="s">
         <v>19</v>
       </c>
       <c r="J3" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K3" s="22"/>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="D4" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="E4" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="F4" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="21" t="s">
+      <c r="H4" s="25" t="s">
         <v>167</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>168</v>
       </c>
       <c r="I4" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J4" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K4" s="22"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="18" t="s">
+      <c r="A5" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="E5" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="F5" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="F5" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G5" s="17" t="s">
+      <c r="H5" s="16" t="s">
         <v>173</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>174</v>
       </c>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K5" s="22"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="A6" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="E6" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="F6" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>179</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>180</v>
       </c>
       <c r="I6" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K6" s="22"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="18" t="s">
+      <c r="A7" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="D7" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="E7" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="F7" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F7" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="H7" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>186</v>
       </c>
       <c r="I7" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K7" s="22"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B8" s="18" t="s">
+      <c r="A8" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="D8" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="E8" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="F8" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="F8" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="17" t="s">
+      <c r="H8" s="16" t="s">
         <v>191</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>192</v>
       </c>
       <c r="I8" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K8" s="22"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B9" s="18" t="s">
+      <c r="A9" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="D9" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="E9" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="F9" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="F9" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="17" t="s">
+      <c r="H9" s="16" t="s">
         <v>197</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>198</v>
       </c>
       <c r="I9" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K9" s="22"/>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B10" s="18" t="s">
+      <c r="A10" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="D10" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="E10" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="F10" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="F10" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="17" t="s">
+      <c r="H10" s="16" t="s">
         <v>203</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>204</v>
       </c>
       <c r="I10" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J10" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K10" s="22"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B11" s="18" t="s">
+      <c r="A11" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="D11" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="E11" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="F11" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="F11" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="17" t="s">
+      <c r="H11" s="16" t="s">
         <v>209</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>210</v>
       </c>
       <c r="I11" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J11" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K11" s="22"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B12" s="18" t="s">
+      <c r="A12" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="D12" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="E12" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="F12" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="17" t="s">
+      <c r="H12" s="16" t="s">
         <v>215</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>216</v>
       </c>
       <c r="I12" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K12" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K12" s="22"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="D13" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="E13" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="F13" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="F13" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="17" t="s">
+      <c r="H13" s="16" t="s">
         <v>221</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>222</v>
       </c>
       <c r="I13" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J13" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K13" s="22"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" s="18" t="s">
+      <c r="A14" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="D14" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="E14" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="E14" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" s="17" t="s">
+      <c r="H14" s="16" t="s">
         <v>226</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>227</v>
       </c>
       <c r="I14" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J14" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K14" s="22"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B15" s="18" t="s">
+      <c r="A15" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="D15" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="E15" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="F15" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="F15" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="17" t="s">
+      <c r="H15" s="16" t="s">
         <v>232</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>233</v>
       </c>
       <c r="I15" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J15" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K15" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K15" s="22"/>
     </row>
     <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B16" s="18" t="s">
+      <c r="A16" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="D16" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="E16" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="F16" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="F16" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="17" t="s">
+      <c r="H16" s="16" t="s">
         <v>238</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>239</v>
       </c>
       <c r="I16" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J16" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K16" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K16" s="22"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B17" s="18" t="s">
+      <c r="A17" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="D17" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="E17" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="F17" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="F17" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="17" t="s">
+      <c r="H17" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>245</v>
       </c>
       <c r="I17" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K17" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K17" s="22"/>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B18" s="18" t="s">
+      <c r="A18" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="D18" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="E18" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="E18" s="25" t="s">
-        <v>249</v>
-      </c>
       <c r="F18" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="H18" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>245</v>
       </c>
       <c r="I18" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K18" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K18" s="22"/>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B19" s="18" t="s">
+      <c r="A19" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="D19" s="29" t="s">
         <v>251</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="E19" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="F19" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="F19" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="17" t="s">
+      <c r="H19" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="H19" s="17" t="s">
+      <c r="I19" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" s="22"/>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="I19" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="J19" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K19" s="24"/>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B20" s="18" t="s">
+      <c r="C20" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="D20" s="29" t="s">
         <v>257</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="E20" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="F20" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="I20" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="K20" s="22"/>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="F20" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="I20" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="J20" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K20" s="24"/>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B21" s="18" t="s">
+      <c r="C21" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="D21" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="E21" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="F21" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="F21" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" s="17" t="s">
+      <c r="H21" s="16" t="s">
         <v>264</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>265</v>
       </c>
       <c r="I21" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J21" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="K21" s="24"/>
+        <v>42</v>
+      </c>
+      <c r="K21" s="22"/>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="17"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="17"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="16"/>
       <c r="D22" s="29"/>
-      <c r="E22" s="17"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="30"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
-      <c r="K22" s="24"/>
+      <c r="K22" s="22"/>
     </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
